--- a/tools/importer/reports/import-product-landing-page.report.xlsx
+++ b/tools/importer/reports/import-product-landing-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="53">
   <si>
     <t>_reportFile</t>
   </si>
@@ -52,7 +52,7 @@
     <t>product-landing-page</t>
   </si>
   <si>
-    <t>2026-06-03T15:58:44.055Z</t>
+    <t>2026-06-07T08:44:20.426Z</t>
   </si>
   <si>
     <t>Home Mortgage Loans &amp; Financing | Wells Fargo</t>
@@ -77,6 +77,99 @@
   </si>
   <si>
     <t>https://www.wellsfargo.com/personal-loans/</t>
+  </si>
+  <si>
+    <t>biz/business-credit.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-image","cards-link-list","cards-icons","accordion","cards-icon-bar","footnotes"]</t>
+  </si>
+  <si>
+    <t>biz/business-credit</t>
+  </si>
+  <si>
+    <t>biz-product</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:07:54.517Z</t>
+  </si>
+  <si>
+    <t>Small Business Loans and Lines of Credit | Wells Fargo</t>
+  </si>
+  <si>
+    <t>https://www.wellsfargo.com/biz/business-credit/</t>
+  </si>
+  <si>
+    <t>biz/merchant.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-image","cards-contact","footnotes"]</t>
+  </si>
+  <si>
+    <t>biz/merchant</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:58:17.892Z</t>
+  </si>
+  <si>
+    <t>Merchant Services, Payment Processing &amp; POS | Wells Fargo</t>
+  </si>
+  <si>
+    <t>https://www.wellsfargo.com/biz/merchant/</t>
+  </si>
+  <si>
+    <t>biz/practice-finance-medical-dental-loans.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-icons","cards-icons","columns","promo","footnotes"]</t>
+  </si>
+  <si>
+    <t>biz/practice-finance-medical-dental-loans</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:09:39.794Z</t>
+  </si>
+  <si>
+    <t>Practice Finance: Medical, Dental, Vet &amp; Optometry Practice Loans | Wells Fargo</t>
+  </si>
+  <si>
+    <t>https://www.wellsfargo.com/biz/practice-finance-medical-dental-loans/</t>
+  </si>
+  <si>
+    <t>biz/sba.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","table-compare","cards-link-list","cards-icons","cards-icon-bar","footnotes"]</t>
+  </si>
+  <si>
+    <t>biz/sba</t>
+  </si>
+  <si>
+    <t>2026-06-08T10:08:47.974Z</t>
+  </si>
+  <si>
+    <t>SBA 7(a) and SBA 504 Loans for Business Financing | Wells Fargo</t>
+  </si>
+  <si>
+    <t>https://www.wellsfargo.com/biz/sba/</t>
+  </si>
+  <si>
+    <t>biz/signify-rewards.report.json</t>
+  </si>
+  <si>
+    <t>["hero-banner","cards-icons","accordion","footnotes"]</t>
+  </si>
+  <si>
+    <t>biz/signify-rewards</t>
+  </si>
+  <si>
+    <t>2026-06-08T11:57:25.361Z</t>
+  </si>
+  <si>
+    <t>Wells Fargo Business Rewards | Signify by Wells Fargo</t>
+  </si>
+  <si>
+    <t>https://www.wellsfargo.com/biz/signify-rewards/</t>
   </si>
 </sst>
 </file>
@@ -465,16 +558,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="43" customWidth="1"/>
     <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="44" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -553,6 +644,136 @@
       </c>
       <c r="H3" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
